--- a/evolucion cedi.xlsx
+++ b/evolucion cedi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SALVAVIDAS\OneDrive - Eficacia\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SALVAVIDAS\OneDrive - Eficacia\Desktop\Escritorio Ismael\ESCRITORIO\KAM\Proyectos IA\Visual Studio\Encuestas HTML\CEDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3418D5-57DD-4881-BD7B-7D8492E4ACA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF14E238-43CF-4D45-850C-838F8F001D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D08C7C17-5568-4CD7-A71D-DF3C31BFFA24}"/>
   </bookViews>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="72">
   <si>
     <t>Año</t>
   </si>
@@ -1042,17 +1042,17 @@
         <v>61</v>
       </c>
       <c r="B16">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="1">
-        <v>69671000</v>
+        <v>63078819</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1078,17 +1078,17 @@
         <v>61</v>
       </c>
       <c r="B18">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="1">
-        <v>37661254</v>
+        <v>45111742</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1096,17 +1096,17 @@
         <v>61</v>
       </c>
       <c r="B19">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C19" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="1">
-        <v>63078819</v>
+        <v>69671000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1132,17 +1132,17 @@
         <v>61</v>
       </c>
       <c r="B21">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="1">
-        <v>45111742</v>
+        <v>37661254</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1205,6 +1205,9 @@
       <c r="F28" s="1">
         <v>3133427530</v>
       </c>
+      <c r="G28" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1225,6 +1228,9 @@
       <c r="F29" s="1">
         <v>339103742</v>
       </c>
+      <c r="G29" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1245,6 +1251,9 @@
       <c r="F30" s="1">
         <v>2293961832</v>
       </c>
+      <c r="G30" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -1265,6 +1274,9 @@
       <c r="F31" s="1">
         <v>715375321</v>
       </c>
+      <c r="G31" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -1285,6 +1297,9 @@
       <c r="F32" s="1">
         <v>2281024189</v>
       </c>
+      <c r="G32" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -1305,6 +1320,9 @@
       <c r="F33" s="1">
         <v>159790551</v>
       </c>
+      <c r="G33" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -1325,6 +1343,9 @@
       <c r="F34" s="1">
         <v>1941208339</v>
       </c>
+      <c r="G34" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -1345,6 +1366,9 @@
       <c r="F35" s="1">
         <v>149440877</v>
       </c>
+      <c r="G35" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -1365,6 +1389,9 @@
       <c r="F36" s="1">
         <v>378989038</v>
       </c>
+      <c r="G36" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -1385,6 +1412,9 @@
       <c r="F37" s="1">
         <v>912279374</v>
       </c>
+      <c r="G37" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -1405,6 +1435,9 @@
       <c r="F38" s="1">
         <v>848376251</v>
       </c>
+      <c r="G38" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -1425,6 +1458,9 @@
       <c r="F39" s="1">
         <v>53490473</v>
       </c>
+      <c r="G39" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1445,6 +1481,9 @@
       <c r="F40" s="1">
         <v>1244371230</v>
       </c>
+      <c r="G40" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -2008,6 +2047,11 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A15:F22">
+    <sortCondition ref="A15:A22"/>
+    <sortCondition ref="B15:B22"/>
+    <sortCondition ref="C15:C22"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/evolucion cedi.xlsx
+++ b/evolucion cedi.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SALVAVIDAS\OneDrive - Eficacia\Desktop\Escritorio Ismael\ESCRITORIO\KAM\Proyectos IA\Visual Studio\Encuestas HTML\CEDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF14E238-43CF-4D45-850C-838F8F001D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8515EFEB-1937-4CF1-8B9C-DFC312F63252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D08C7C17-5568-4CD7-A71D-DF3C31BFFA24}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja4" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Hoja3" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$27:$F$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$30:$F$40</definedName>
+    <definedName name="SegmentaciónDeDatos_Canal1">#N/A</definedName>
+    <definedName name="SegmentaciónDeDatos_Canal2">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
+      <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicerCache r:id="rId5"/>
+        <x14:slicerCache r:id="rId6"/>
+      </x15:slicerCaches>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -39,80 +52,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="6">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="6">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
-    <bk>
-      <rc t="1" v="4"/>
-    </bk>
-    <bk>
-      <rc t="1" v="5"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="76">
   <si>
     <t>Año</t>
   </si>
@@ -291,9 +232,6 @@
     <t>Almacenamiento</t>
   </si>
   <si>
-    <t># Pedidos</t>
-  </si>
-  <si>
     <t># Posiciones</t>
   </si>
   <si>
@@ -309,9 +247,6 @@
     <t>3-6 meses</t>
   </si>
   <si>
-    <t>Observaciones</t>
-  </si>
-  <si>
     <t>Rango</t>
   </si>
   <si>
@@ -327,7 +262,25 @@
     <t>&gt;12 meses</t>
   </si>
   <si>
-    <t>TT- CARAMELERA TRIDENT 2025 / TT KIWI 2 BANDEJAS 2025 / TT JANUS SEMIPERMANENTE 2025 / TT NUEVO EXHIBIDOR TRIDENT 5 BANDEJAS / TT CAJERO VENDEDOR HALLS X 5 / TT EXHIBIDOR SFC 3X2</t>
+    <t>Total Canales</t>
+  </si>
+  <si>
+    <t>Columna1</t>
+  </si>
+  <si>
+    <t>Columna2</t>
+  </si>
+  <si>
+    <t>Orden rango</t>
+  </si>
+  <si>
+    <t>% Part</t>
+  </si>
+  <si>
+    <t>Posiciones</t>
+  </si>
+  <si>
+    <t>Valor Posición</t>
   </si>
 </sst>
 </file>
@@ -338,7 +291,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,16 +314,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -378,22 +357,177 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -406,93 +540,2653 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja4!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cantidad</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inBase"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Hoja4!$A$2:$E$11</c15:sqref>
+                  </c15:fullRef>
+                  <c15:levelRef>
+                    <c15:sqref>Hoja4!$C$2:$C$11</c15:sqref>
+                  </c15:levelRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Hoja4!$C$2:$C$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0-1 mes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1-3 meses</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3-6 meses</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6-12 meses</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>&gt;12 meses</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja4!$F$2:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9619</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8168</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7030</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9AC4-43E5-B5E5-01BB5E58B248}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="515754896"/>
+        <c:axId val="515753096"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja4!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Valor Inventario</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Hoja4!$A$2:$E$11</c15:sqref>
+                  </c15:fullRef>
+                  <c15:levelRef>
+                    <c15:sqref>Hoja4!$C$2:$C$11</c15:sqref>
+                  </c15:levelRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Hoja4!$C$2:$C$11</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0-1 mes</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1-3 meses</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3-6 meses</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6-12 meses</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>&gt;12 meses</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja4!$G$2:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>_-"$"\ * #,##0_-;\-"$"\ * #,##0_-;_-"$"\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>149440877</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>143764796</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>77016131</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7846428</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9AC4-43E5-B5E5-01BB5E58B248}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="591098976"/>
+        <c:axId val="591097896"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="515754896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="515753096"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="515753096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="515754896"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="591097896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="591098976"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="591098976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="591097896"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>3</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>4</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>5</v>
-    <v>5</v>
-  </rv>
-</rvData>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja3!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Facturación</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Hoja3!$A$2:$D$13</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="4"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Tradicional</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Tradicional</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Tradicional</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Tradicional</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Diciembre</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Diciembre</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Enero</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Enero</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2024</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>2025</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>2025</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>2026</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Transporte</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Transporte</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Transporte</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Transporte</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja3!$E$2:$E$13</c:f>
+              <c:numCache>
+                <c:formatCode>_-"$"\ * #,##0_-;\-"$"\ * #,##0_-;_-"$"\ * "-"??_-;_-@_-</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>82485131</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>225685382</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69671000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>37661254</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0CA5-41EA-9887-00398B4CDD45}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="743279488"/>
+        <c:axId val="743280568"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Hoja3!$F$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Columna1</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Hoja3!$A$2:$D$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="4"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Diciembre</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>Diciembre</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>Enero</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>Enero</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>2024</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>2025</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>2025</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>2026</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                      </c:lvl>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Hoja3!$F$2:$F$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0%</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1.7360735112368313</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>-0.69129148116469497</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>-0.45944146057900703</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-0CA5-41EA-9887-00398B4CDD45}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Hoja3!$G$1</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>Columna2</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent3"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Hoja3!$A$2:$D$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="4"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>Tradicional</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Diciembre</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>Diciembre</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>Enero</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>Enero</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>2024</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>2025</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>2025</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>2026</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>Transporte</c:v>
+                        </c:pt>
+                      </c:lvl>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Hoja3!$G$2:$G$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="3" formatCode="0%">
+                        <c:v>-0.83312497395156948</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-0CA5-41EA-9887-00398B4CDD45}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="743279488"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="743280568"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="743280568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="743279488"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
 </file>
 
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-  <rel r:id="rId3"/>
-  <rel r:id="rId4"/>
-  <rel r:id="rId5"/>
-  <rel r:id="rId6"/>
-</richValueRels>
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CDAB178-715E-1E9C-3C40-7B620B3E7273}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>89535</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Canal 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40C12DBF-B7B8-4AFB-EBFA-EE843BF59ACC}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Canal 2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7170420" y="2446020"/>
+              <a:ext cx="1828800" cy="2581275"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100"/>
+                <a:t>Esta forma representa una segmentación de tabla. Las segmentaciones de tabla no se admiten en esta versión de Excel.
+Si la forma se modificó en una versión anterior de Excel o si el libro se guardó en Excel 2007 o en una versión anterior, no se podrá usar la segmentación.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>60960</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>20955</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer" Requires="sle15">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Canal 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1F61EF2-CDF0-6D27-D37F-BD5F9648DC3E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Canal 1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="60960" y="2743200"/>
+              <a:ext cx="1828800" cy="2581275"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="es-CO" sz="1100"/>
+                <a:t>Esta forma representa una segmentación de tabla. Las segmentaciones de tabla no se admiten en esta versión de Excel.
+Si la forma se modificó en una versión anterior de Excel o si el libro se guardó en Excel 2007 o en una versión anterior, no se podrá usar la segmentación.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4904DF3-F23D-77F4-93EF-D1D50E2CEFF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaciónDeDatos_Canal1" xr10:uid="{7CB9744A-F2EE-4D7A-AE49-A6F86783761D}" sourceName="Canal">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="2" column="4"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaciónDeDatos_Canal2" xr10:uid="{C6381C23-FEE9-4F38-A608-85E56377A185}" sourceName="Canal">
+  <extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
+      <x15:tableSlicerCache tableId="3" column="4"/>
+    </x:ext>
+  </extLst>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Canal 2" xr10:uid="{5DBCCD98-FCEF-4F20-A951-C39114C01301}" cache="SegmentaciónDeDatos_Canal2" caption="Canal" rowHeight="247650"/>
+</slicers>
+</file>
+
+<file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Canal 1" xr10:uid="{75EF51F6-05C7-4F92-AD1E-C09CCBDEC204}" cache="SegmentaciónDeDatos_Canal1" caption="Canal" rowHeight="247650"/>
+</slicers>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5CE3FEF3-24CE-4C40-9D70-4EF8DFE0A7F7}" name="Tabla1" displayName="Tabla1" ref="A2:F10" totalsRowShown="0">
+  <autoFilter ref="A2:F10" xr:uid="{5CE3FEF3-24CE-4C40-9D70-4EF8DFE0A7F7}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{AFB5A9F0-2654-417C-B0D5-27564B0FBFFD}" name="Indicador"/>
+    <tableColumn id="2" xr3:uid="{545E9B83-EF34-4609-8FBC-732280492E15}" name="Año"/>
+    <tableColumn id="3" xr3:uid="{3183BDD3-13DE-418A-9351-323B188C626F}" name="Mes"/>
+    <tableColumn id="4" xr3:uid="{D152D224-AB0E-4CE0-9B03-418ACE35ACAA}" name="Canal"/>
+    <tableColumn id="5" xr3:uid="{9EFB9666-4780-44F6-9A5A-37E7C39A06FB}" name="# Posiciones" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{F4D0A00E-A812-4904-B194-84CD77BA4D10}" name="Facturación" dataDxfId="5" dataCellStyle="Moneda"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{0C8E102B-3F20-45CB-BF1E-99B10E930260}" name="Tabla3" displayName="Tabla3" ref="A1:G11" totalsRowShown="0">
+  <autoFilter ref="A1:G11" xr:uid="{0C8E102B-3F20-45CB-BF1E-99B10E930260}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Moderno"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G11">
+    <sortCondition ref="A2:A11"/>
+    <sortCondition ref="B2:B11"/>
+    <sortCondition ref="E2:E11"/>
+  </sortState>
+  <tableColumns count="7">
+    <tableColumn id="4" xr3:uid="{FC3F1DD2-81D2-4322-865E-4CDDEEB5A486}" name="Canal"/>
+    <tableColumn id="7" xr3:uid="{7CE3EB69-14B6-4CC3-9F67-B7C7B7A9031F}" name="Orden rango"/>
+    <tableColumn id="1" xr3:uid="{9E8A07B1-C606-47BE-91E8-01126A9CA192}" name="Rango"/>
+    <tableColumn id="2" xr3:uid="{02F685B3-FC72-4371-855A-9390E47D88E8}" name="Año"/>
+    <tableColumn id="3" xr3:uid="{3090BCE7-0BCB-4DD1-ACDF-5D73FD955982}" name="Mes"/>
+    <tableColumn id="5" xr3:uid="{E5772E85-05B7-4E85-AA35-84453346BF01}" name="Cantidad" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{D7B6F5EA-1492-41CA-A130-3C2F9FD23044}" name="Valor Inventario" dataDxfId="0" dataCellStyle="Moneda"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2FB7CB75-42B3-4C09-8617-C046E589E6FF}" name="Tabla2" displayName="Tabla2" ref="A1:G13" totalsRowShown="0">
+  <autoFilter ref="A1:G13" xr:uid="{2FB7CB75-42B3-4C09-8617-C046E589E6FF}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Tradicional"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{10C07BF9-443D-4995-8932-C44E8D426D3F}" name="Indicador"/>
+    <tableColumn id="2" xr3:uid="{CCA48BDB-F2F4-4771-BC22-C4855A5B72E3}" name="Año"/>
+    <tableColumn id="3" xr3:uid="{551FB4E3-E4FB-466A-9F53-BAFA65D5934D}" name="Mes"/>
+    <tableColumn id="4" xr3:uid="{DA1C07A4-82B7-4903-8806-C865BB250263}" name="Canal" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{D06C9101-4006-44B8-B3EC-059062D455BB}" name="Facturación" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{BCC0A720-7528-4973-8293-8C9A60EED877}" name="Columna1" dataDxfId="2" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula>(E2-E1)/E1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{71310D9C-189B-41C9-B49C-EB1253792BB5}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -812,11 +3506,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2F1800-0519-45C4-A152-3381840088AA}">
-  <dimension ref="A2:G67"/>
+  <dimension ref="A2:G40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.6640625" customWidth="1"/>
-    <col min="7" max="7" width="25.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -833,7 +3528,7 @@
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
@@ -999,334 +3694,266 @@
         <v>3468993</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15">
-        <v>2024</v>
-      </c>
-      <c r="C15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="1">
-        <v>82485131</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16">
-        <v>2024</v>
-      </c>
-      <c r="C16" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="1">
-        <v>63078819</v>
-      </c>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E11" s="2"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E13" s="2"/>
+      <c r="F13" s="1"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17">
-        <v>2025</v>
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="1">
-        <v>225685382</v>
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="1">
-        <v>45111742</v>
+        <v>7</v>
+      </c>
+      <c r="E18" s="1">
+        <v>82485131</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="1">
-        <v>69671000</v>
+        <v>6</v>
+      </c>
+      <c r="E19" s="1">
+        <v>63078819</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20">
         <v>2025</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="1">
-        <v>11356591</v>
+        <v>7</v>
+      </c>
+      <c r="E20" s="1">
+        <v>225685382</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="1">
-        <v>37661254</v>
+        <v>6</v>
+      </c>
+      <c r="E21" s="1">
+        <v>45111742</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
       </c>
       <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1">
+        <v>69671000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23">
+        <v>2025</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="1">
+      <c r="E23" s="1">
+        <v>11356591</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24">
+        <v>2026</v>
+      </c>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1">
+        <v>37661254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25">
+        <v>2026</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1">
         <v>44147117</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" t="s">
-        <v>62</v>
-      </c>
-      <c r="F27" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28">
-        <v>2024</v>
-      </c>
-      <c r="C28" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2">
-        <v>332160</v>
-      </c>
-      <c r="F28" s="1">
-        <v>3133427530</v>
-      </c>
-      <c r="G28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29">
-        <v>2024</v>
-      </c>
-      <c r="C29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="2">
-        <v>21159</v>
-      </c>
-      <c r="F29" s="1">
-        <v>339103742</v>
-      </c>
-      <c r="G29" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30">
-        <v>2025</v>
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2">
-        <v>273517</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2293961832</v>
+        <v>5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" t="s">
+        <v>62</v>
       </c>
       <c r="G30" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B31">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E31" s="2">
-        <v>20773</v>
+        <v>420</v>
       </c>
       <c r="F31" s="1">
-        <v>715375321</v>
-      </c>
-      <c r="G31" t="s">
-        <v>71</v>
+        <v>1941208339</v>
+      </c>
+      <c r="G31" s="1">
+        <v>26140771.273373052</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B32">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C32" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" s="2">
-        <v>193143</v>
+        <v>16</v>
       </c>
       <c r="F32" s="1">
-        <v>2281024189</v>
-      </c>
-      <c r="G32" t="s">
-        <v>71</v>
+        <v>149440877</v>
+      </c>
+      <c r="G32" s="1">
+        <v>979712.5201472909</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33" s="2">
-        <v>8763</v>
+        <v>248.22740437010151</v>
       </c>
       <c r="F33" s="1">
-        <v>159790551</v>
-      </c>
-      <c r="G33" t="s">
-        <v>71</v>
+        <v>1012707863</v>
+      </c>
+      <c r="G33" s="1">
+        <v>15433787.094115425</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B34">
         <v>2026</v>
@@ -1335,21 +3962,21 @@
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2">
-        <v>541495</v>
+        <v>93</v>
       </c>
       <c r="F34" s="1">
-        <v>1941208339</v>
-      </c>
-      <c r="G34" t="s">
-        <v>71</v>
+        <v>143764796</v>
+      </c>
+      <c r="G34" s="1">
+        <v>5758132.6989545925</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B35">
         <v>2026</v>
@@ -1358,85 +3985,85 @@
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E35" s="2">
-        <v>9619</v>
+        <v>44.312100261374376</v>
       </c>
       <c r="F35" s="1">
-        <v>149440877</v>
-      </c>
-      <c r="G35" t="s">
-        <v>71</v>
+        <v>138125217</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2755149.1458512121</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B36">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C36" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2">
-        <v>35526</v>
+        <v>18</v>
       </c>
       <c r="F36" s="1">
-        <v>378989038</v>
-      </c>
-      <c r="G36" t="s">
-        <v>71</v>
+        <v>77016131</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1094281.4141226669</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B37">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C37" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E37" s="2">
-        <v>2909</v>
+        <v>29.218219888534659</v>
       </c>
       <c r="F37" s="1">
-        <v>912279374</v>
-      </c>
-      <c r="G37" t="s">
-        <v>71</v>
+        <v>93010431</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1816672.0397895304</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B38">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2">
-        <v>89664</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1">
-        <v>848376251</v>
-      </c>
-      <c r="G38" t="s">
-        <v>71</v>
+        <v>7846428</v>
+      </c>
+      <c r="G38" s="1">
+        <v>71199.202455029939</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1444,22 +4071,22 @@
         <v>68</v>
       </c>
       <c r="B39">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39" s="2">
-        <v>16186</v>
+        <v>7.0523708622352519</v>
       </c>
       <c r="F39" s="1">
-        <v>53490473</v>
-      </c>
-      <c r="G39" t="s">
-        <v>71</v>
+        <v>20883129</v>
+      </c>
+      <c r="G39" s="1">
+        <v>438488.21073033899</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -1467,596 +4094,387 @@
         <v>68</v>
       </c>
       <c r="B40">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C40" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="2">
-        <v>361449</v>
+        <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>1244371230</v>
-      </c>
-      <c r="G40" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>68</v>
-      </c>
-      <c r="B41">
-        <v>2025</v>
-      </c>
-      <c r="C41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="2">
-        <v>19585</v>
-      </c>
-      <c r="F41" s="1">
-        <v>292886357</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>68</v>
-      </c>
-      <c r="B42">
-        <v>2026</v>
-      </c>
-      <c r="C42" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="2">
-        <v>137626</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1012707863</v>
-      </c>
-      <c r="G42" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43">
-        <v>2026</v>
-      </c>
-      <c r="C43" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="2">
-        <v>8168</v>
-      </c>
-      <c r="F43" s="1">
-        <v>143764796</v>
-      </c>
-      <c r="G43" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44">
-        <v>2024</v>
-      </c>
-      <c r="C44" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="2">
-        <v>442941</v>
-      </c>
-      <c r="F44" s="1">
-        <v>429317072</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>64</v>
-      </c>
-      <c r="B45">
-        <v>2024</v>
-      </c>
-      <c r="C45" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="2">
-        <v>11627</v>
-      </c>
-      <c r="F45" s="1">
-        <v>596965328</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>64</v>
-      </c>
-      <c r="B46">
-        <v>2025</v>
-      </c>
-      <c r="C46" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="2">
-        <v>393381</v>
-      </c>
-      <c r="F46" s="1">
-        <v>380197897</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47">
-        <v>2025</v>
-      </c>
-      <c r="C47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47" s="2">
-        <v>7167</v>
-      </c>
-      <c r="F47" s="1">
-        <v>737315843</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48">
-        <v>2025</v>
-      </c>
-      <c r="C48" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2">
-        <v>42505</v>
-      </c>
-      <c r="F48" s="1">
-        <v>98308159</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>64</v>
-      </c>
-      <c r="B49">
-        <v>2025</v>
-      </c>
-      <c r="C49" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="2">
-        <v>2080</v>
-      </c>
-      <c r="F49" s="1">
-        <v>53142120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50">
-        <v>2026</v>
-      </c>
-      <c r="C50" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="2">
-        <v>13088</v>
-      </c>
-      <c r="F50" s="1">
-        <v>138125217</v>
-      </c>
-      <c r="G50" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>64</v>
-      </c>
-      <c r="B51">
-        <v>2026</v>
-      </c>
-      <c r="C51" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="2">
-        <v>7030</v>
-      </c>
-      <c r="F51" s="1">
-        <v>77016131</v>
-      </c>
-      <c r="G51" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52">
-        <v>2024</v>
-      </c>
-      <c r="C52" t="s">
-        <v>3</v>
-      </c>
-      <c r="D52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="2">
-        <v>69519</v>
-      </c>
-      <c r="F52" s="1">
-        <v>702641141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B53">
-        <v>2024</v>
-      </c>
-      <c r="C53" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="2">
-        <v>9132</v>
-      </c>
-      <c r="F53" s="1">
-        <v>172904363</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-      <c r="B54">
-        <v>2025</v>
-      </c>
-      <c r="C54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="2">
-        <v>51664</v>
-      </c>
-      <c r="F54" s="1">
-        <v>679579299</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55">
-        <v>2025</v>
-      </c>
-      <c r="C55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="2">
-        <v>11055</v>
-      </c>
-      <c r="F55" s="1">
-        <v>363019502</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56">
-        <v>2025</v>
-      </c>
-      <c r="C56" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="2">
-        <v>15281</v>
-      </c>
-      <c r="F56" s="1">
-        <v>71555718</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>69</v>
-      </c>
-      <c r="B57">
-        <v>2025</v>
-      </c>
-      <c r="C57" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="2">
-        <v>348</v>
-      </c>
-      <c r="F57" s="1">
-        <v>6223028</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>69</v>
-      </c>
-      <c r="B58">
-        <v>2026</v>
-      </c>
-      <c r="C58" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="2">
-        <v>16067</v>
-      </c>
-      <c r="F58" s="1">
-        <v>93010431</v>
-      </c>
-      <c r="G58" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59">
-        <v>2026</v>
-      </c>
-      <c r="C59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="2">
-        <v>455</v>
-      </c>
-      <c r="F59" s="1">
-        <v>7846428</v>
-      </c>
-      <c r="G59" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60">
-        <v>2024</v>
-      </c>
-      <c r="C60" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="2">
-        <v>7473</v>
-      </c>
-      <c r="F60" s="1">
-        <v>78556001</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>70</v>
-      </c>
-      <c r="B61">
-        <v>2024</v>
-      </c>
-      <c r="C61" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="2">
-        <v>38579</v>
-      </c>
-      <c r="F61" s="1">
-        <v>142129307</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62">
-        <v>2025</v>
-      </c>
-      <c r="C62" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="2">
-        <v>24524</v>
-      </c>
-      <c r="F62" s="1">
-        <v>151624104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63">
-        <v>2025</v>
-      </c>
-      <c r="C63" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63" s="2">
-        <v>37363</v>
-      </c>
-      <c r="F63" s="1">
-        <v>116812412</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64">
-        <v>2025</v>
-      </c>
-      <c r="C64" t="s">
-        <v>3</v>
-      </c>
-      <c r="D64" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="2">
-        <v>89</v>
-      </c>
-      <c r="F64" s="1">
-        <v>4602133</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>70</v>
-      </c>
-      <c r="B65">
-        <v>2025</v>
-      </c>
-      <c r="C65" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65" s="2">
         <v>0</v>
       </c>
-      <c r="F65" s="1">
+      <c r="G40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>70</v>
-      </c>
-      <c r="B66">
-        <v>2026</v>
-      </c>
-      <c r="C66" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" s="2">
-        <v>4082</v>
-      </c>
-      <c r="F66" s="1">
-        <v>20883129</v>
-      </c>
-      <c r="G66" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67">
-        <v>2026</v>
-      </c>
-      <c r="C67" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67" s="2">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A15:F22">
-    <sortCondition ref="A15:A22"/>
-    <sortCondition ref="B15:B22"/>
-    <sortCondition ref="C15:C22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A18:F25">
+    <sortCondition ref="A18:A25"/>
+    <sortCondition ref="B18:B25"/>
+    <sortCondition ref="C18:C25"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43FF129-0A71-49A7-BB93-049204AA2A86}">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2">
+        <v>9619</v>
+      </c>
+      <c r="G2" s="1">
+        <v>149440877</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3">
+        <v>2026</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8168</v>
+      </c>
+      <c r="G3" s="1">
+        <v>143764796</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>7030</v>
+      </c>
+      <c r="G4" s="1">
+        <v>77016131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5">
+        <v>2026</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>455</v>
+      </c>
+      <c r="G5" s="1">
+        <v>7846428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6">
+        <v>2026</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7">
+        <v>2026</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>541495</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1941208339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8">
+        <v>2026</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>137626</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1012707863</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9">
+        <v>2026</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>13088</v>
+      </c>
+      <c r="G9" s="1">
+        <v>138125217</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10">
+        <v>2026</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>16067</v>
+      </c>
+      <c r="G10" s="1">
+        <v>93010431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11">
+        <v>2026</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4082</v>
+      </c>
+      <c r="G11" s="1">
+        <v>20883129</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="11">
+        <v>149440877</v>
+      </c>
+      <c r="D19" s="12">
+        <v>143764796</v>
+      </c>
+      <c r="E19" s="11">
+        <v>77016131</v>
+      </c>
+      <c r="F19" s="12">
+        <v>7846428</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="7">
+        <f>SUM(C19:G19)</f>
+        <v>378068232</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="13">
+        <f>C19/$H$19</f>
+        <v>0.39527488519585535</v>
+      </c>
+      <c r="D21" s="13">
+        <f t="shared" ref="D21:G21" si="0">D19/$H$19</f>
+        <v>0.38026150792801866</v>
+      </c>
+      <c r="E21" s="13">
+        <f t="shared" si="0"/>
+        <v>0.20370960710605276</v>
+      </c>
+      <c r="F21" s="13">
+        <f t="shared" si="0"/>
+        <v>2.075399977007325E-2</v>
+      </c>
+      <c r="G21" s="13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
+      <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DFA9F3-E102-4B5A-93C5-F6C0684EBD9C}">
   <dimension ref="A2:A63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2309,4 +4727,321 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C12686CB-029F-4405-A3B2-E96922BA56DE}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2">
+        <v>2024</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1">
+        <v>82485131</v>
+      </c>
+      <c r="F2" s="9" t="e">
+        <f>(E2-E1)/E1</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>63078819</v>
+      </c>
+      <c r="F3" s="10">
+        <f>(E3-E2)/E2</f>
+        <v>-0.23527042710279505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4">
+        <v>2025</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1">
+        <v>225685382</v>
+      </c>
+      <c r="F4" s="9">
+        <f>(E4-E2)/E2</f>
+        <v>1.7360735112368313</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5">
+        <v>2025</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="1">
+        <v>45111742</v>
+      </c>
+      <c r="F5" s="10">
+        <f>(E5-E3)/E3</f>
+        <v>-0.28483534227234025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6">
+        <v>2025</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1">
+        <v>69671000</v>
+      </c>
+      <c r="F6" s="9">
+        <f>(E6-E4)/E4</f>
+        <v>-0.69129148116469497</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7">
+        <v>2025</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1">
+        <v>11356591</v>
+      </c>
+      <c r="F7" s="10">
+        <f>(E7-E6)/E6</f>
+        <v>-0.83699687100802345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8">
+        <v>2026</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>37661254</v>
+      </c>
+      <c r="F8" s="9">
+        <f>(E8-E6)/E6</f>
+        <v>-0.45944146057900703</v>
+      </c>
+      <c r="G8" s="8">
+        <f>(E8-E4)/E4</f>
+        <v>-0.83312497395156948</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9">
+        <v>2026</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1">
+        <v>44147117</v>
+      </c>
+      <c r="F9" s="10">
+        <f>(E9-E7)/E7</f>
+        <v>2.8873564258851974</v>
+      </c>
+      <c r="G9" s="8">
+        <f>(E9-E5)/E5</f>
+        <v>-2.1383013761694238E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10">
+        <v>2024</v>
+      </c>
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="7">
+        <f>E2+E3</f>
+        <v>145563950</v>
+      </c>
+      <c r="F10" s="9">
+        <f>(E10-E9)/E9</f>
+        <v>2.2972470206831401</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11">
+        <v>2025</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="7">
+        <f>E4+E5</f>
+        <v>270797124</v>
+      </c>
+      <c r="F11" s="10">
+        <f>(E11-E10)/E10</f>
+        <v>0.86033096793539887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12">
+        <v>2025</v>
+      </c>
+      <c r="C12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="7">
+        <f>E6+E7</f>
+        <v>81027591</v>
+      </c>
+      <c r="F12" s="9">
+        <f>(E12-E11)/E11</f>
+        <v>-0.70078119810460027</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13">
+        <v>2026</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="7">
+        <f>E8+E9</f>
+        <v>81808371</v>
+      </c>
+      <c r="F13" s="10">
+        <f>(E13-E12)/E12</f>
+        <v>9.6359769599962553E-3</v>
+      </c>
+      <c r="G13" s="8">
+        <f>(E13-E11)/E11</f>
+        <v>-0.6978979326235385</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{3A4CF648-6AED-40f4-86FF-DC5316D8AED3}">
+      <x14:slicerList xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
 </file>